--- a/files/港岛-北角-101 Kings Road.xlsx
+++ b/files/港岛-北角-101 Kings Road.xlsx
@@ -1519,38 +1519,30 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>19198000</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>33799</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K15" s="5" t="n">
+        <v>19198000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>33799</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1559,7 +1551,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16422,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -16440,7 +16432,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -16577,12 +16569,12 @@
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
-招标单位
--
-(在售)</t>
+$1920万
+$33,799/呎
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">

--- a/files/港岛-北角-101 Kings Road.xlsx
+++ b/files/港岛-北角-101 Kings Road.xlsx
@@ -16097,38 +16097,30 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H250" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I250" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H250" s="5" t="n">
+        <v>16080000</v>
+      </c>
+      <c r="I250" s="5" t="n">
+        <v>40000</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K250" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L250" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K250" s="5" t="n">
+        <v>16080000</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>40000</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -16137,7 +16129,7 @@
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16414,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -16432,7 +16424,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18632,12 +18624,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 402呎 (2房)
-招标单位
--
-(在售)</t>
+$1608万
+$40,000/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">

--- a/files/港岛-北角-101 Kings Road.xlsx
+++ b/files/港岛-北角-101 Kings Road.xlsx
@@ -116,13 +116,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -261,10 +261,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -953,38 +953,30 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>64550000</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>50000</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K6" s="5" t="n">
+        <v>64550000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>50000</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -993,7 +985,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5867,34 +5859,34 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
-        <v>19016000</v>
+        <v>15023000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>43218</v>
+        <v>34143</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="5" t="n">
-        <v>15022640</v>
+        <v>15023000</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>34142</v>
+        <v>34143</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
@@ -16414,7 +16406,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -16424,7 +16416,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>247</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -16509,12 +16501,12 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1291呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
+$6455万
+$50,000/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 877呎 (3房)
 $4210万
@@ -16522,7 +16514,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>C | 1119呎 (3房)
 招标单位
@@ -16530,7 +16522,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 861呎 (3房)
 $4133万
@@ -16552,7 +16544,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
 招标单位
@@ -16561,7 +16553,7 @@
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1920万
@@ -16569,7 +16561,7 @@
 (26年-09月-08日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1471万
@@ -16577,7 +16569,7 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $972万
@@ -16585,7 +16577,7 @@
 (25年-09月-29日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $655万
@@ -16593,7 +16585,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $967万
@@ -16601,7 +16593,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $1050万
@@ -16609,7 +16601,7 @@
 (25年-10月-24日)</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $648万
@@ -16617,7 +16609,7 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $1064万
@@ -16625,7 +16617,7 @@
 (26年-02月-11日)</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1187万
@@ -16640,7 +16632,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
 $3101万
@@ -16649,7 +16641,7 @@
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1913万
@@ -16657,7 +16649,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1459万
@@ -16665,7 +16657,7 @@
 (26年-03月-10日)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $956万
@@ -16673,7 +16665,7 @@
 (25年-10月-28日)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $646万
@@ -16681,7 +16673,7 @@
 (24年-12月-31日)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $928万
@@ -16689,7 +16681,7 @@
 (25年-08月-07日)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $1037万
@@ -16697,7 +16689,7 @@
 (24年-12月-13日)</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $640万
@@ -16705,7 +16697,7 @@
 (25年-01月-20日)</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $1054万
@@ -16713,7 +16705,7 @@
 (26年-02月-05日)</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1226万
@@ -16728,7 +16720,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
 $3017万
@@ -16737,7 +16729,7 @@
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr"/>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1851万
@@ -16745,7 +16737,7 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1446万
@@ -16753,7 +16745,7 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $940万
@@ -16761,7 +16753,7 @@
 (25年-11月-07日)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $644万
@@ -16769,7 +16761,7 @@
 (25年-01月-03日)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $924万
@@ -16777,7 +16769,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $1034万
@@ -16785,7 +16777,7 @@
 (25年-10月-16日)</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $632万
@@ -16793,7 +16785,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $1043万
@@ -16801,7 +16793,7 @@
 (25年-12月-18日)</t>
         </is>
       </c>
-      <c r="L8" s="21" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1164万
@@ -16816,7 +16808,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
 $2944万
@@ -16825,7 +16817,7 @@
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr"/>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1750万
@@ -16833,7 +16825,7 @@
 (25年-04月-09日)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1433万
@@ -16841,7 +16833,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $926万
@@ -16849,7 +16841,7 @@
 (25年-11月-11日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $634万
@@ -16857,7 +16849,7 @@
 (24年-12月-30日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $912万
@@ -16865,7 +16857,7 @@
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $1017万
@@ -16873,7 +16865,7 @@
 (25年-05月-06日)</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $642万
@@ -16881,7 +16873,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $1033万
@@ -16889,7 +16881,7 @@
 (26年-01月-13日)</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1153万
@@ -16904,7 +16896,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
 $2933万
@@ -16913,7 +16905,7 @@
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr"/>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1743万
@@ -16921,7 +16913,7 @@
 (25年-11月-04日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1480万
@@ -16929,7 +16921,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $912万
@@ -16937,7 +16929,7 @@
 (25年-10月-23日)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $625万
@@ -16945,7 +16937,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $899万
@@ -16953,7 +16945,7 @@
 (25年-10月-27日)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $1028万
@@ -16961,7 +16953,7 @@
 (25年-02月-17日)</t>
         </is>
       </c>
-      <c r="J10" s="21" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $634万
@@ -16969,7 +16961,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $1008万
@@ -16977,7 +16969,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1142万
@@ -16992,7 +16984,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
 $2430万
@@ -17001,7 +16993,7 @@
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr"/>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1704万
@@ -17009,7 +17001,7 @@
 (26年-02月-03日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1409万
@@ -17017,7 +17009,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $898万
@@ -17025,7 +17017,7 @@
 (25年-10月-27日)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $599万
@@ -17033,7 +17025,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $886万
@@ -17041,7 +17033,7 @@
 (25年-09月-16日)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $1010万
@@ -17049,7 +17041,7 @@
 (24年-12月-16日)</t>
         </is>
       </c>
-      <c r="J11" s="21" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $627万
@@ -17057,7 +17049,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="K11" s="21" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $1012万
@@ -17065,7 +17057,7 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="L11" s="21" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1130万
@@ -17080,7 +17072,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1653万
@@ -17088,7 +17080,7 @@
 (26年-02月-05日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $866万
@@ -17096,7 +17088,7 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1669万
@@ -17104,7 +17096,7 @@
 (25年-12月-22日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1512万
@@ -17112,7 +17104,7 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $885万
@@ -17120,7 +17112,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $607万
@@ -17128,7 +17120,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $898万
@@ -17136,7 +17128,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $964万
@@ -17144,7 +17136,7 @@
 (24年-12月-13日)</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $619万
@@ -17152,7 +17144,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $1002万
@@ -17160,7 +17152,7 @@
 (25年-12月-08日)</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1119万
@@ -17175,7 +17167,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1637万
@@ -17183,7 +17175,7 @@
 (26年-03月-05日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $857万
@@ -17191,7 +17183,7 @@
 (26年-01月-19日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1636万
@@ -17202,12 +17194,12 @@
       <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
-$1902万
-$43,218/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
+$1502万
+$34,143/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $903万
@@ -17215,7 +17207,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $584万
@@ -17223,7 +17215,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $888万
@@ -17231,7 +17223,7 @@
 (24年-12月-10日)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $956万
@@ -17239,7 +17231,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $594万
@@ -17247,7 +17239,7 @@
 (24年-12月-20日)</t>
         </is>
       </c>
-      <c r="K13" s="21" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $951万
@@ -17255,7 +17247,7 @@
 (25年-11月-14日)</t>
         </is>
       </c>
-      <c r="L13" s="21" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1108万
@@ -17270,7 +17262,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1584万
@@ -17278,7 +17270,7 @@
 (25年-02月-21日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $847万
@@ -17286,7 +17278,7 @@
 (26年-01月-16日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1590万
@@ -17294,7 +17286,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1422万
@@ -17302,7 +17294,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $871万
@@ -17310,7 +17302,7 @@
 (25年-03月-13日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $595万
@@ -17318,7 +17310,7 @@
 (25年-01月-02日)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $877万
@@ -17326,7 +17318,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $975万
@@ -17334,7 +17326,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $605万
@@ -17342,7 +17334,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $941万
@@ -17350,7 +17342,7 @@
 (25年-11月-11日)</t>
         </is>
       </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1129万
@@ -17365,7 +17357,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1618万
@@ -17373,7 +17365,7 @@
 (26年-02月-23日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $837万
@@ -17381,7 +17373,7 @@
 (26年-01月-07日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1565万
@@ -17389,7 +17381,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1343万
@@ -17397,7 +17389,7 @@
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $889万
@@ -17405,7 +17397,7 @@
 (24年-12月-10日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $573万
@@ -17413,7 +17405,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $867万
@@ -17421,7 +17413,7 @@
 (24年-12月-10日)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $966万
@@ -17429,7 +17421,7 @@
 (24年-12月-10日)</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $599万
@@ -17437,7 +17429,7 @@
 (24年-12月-20日)</t>
         </is>
       </c>
-      <c r="K15" s="21" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $958万
@@ -17445,7 +17437,7 @@
 (25年-02月-06日)</t>
         </is>
       </c>
-      <c r="L15" s="21" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1087万
@@ -17460,7 +17452,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1583万
@@ -17468,7 +17460,7 @@
 (26年-01月-05日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $828万
@@ -17476,7 +17468,7 @@
 (26年-01月-07日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1535万
@@ -17484,7 +17476,7 @@
 (25年-08月-15日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1321万
@@ -17492,7 +17484,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $858万
@@ -17500,7 +17492,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $584万
@@ -17508,7 +17500,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $856万
@@ -17516,7 +17508,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $958万
@@ -17524,7 +17516,7 @@
 (24年-12月-13日)</t>
         </is>
       </c>
-      <c r="J16" s="21" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $593万
@@ -17532,7 +17524,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="K16" s="21" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $948万
@@ -17540,7 +17532,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="L16" s="21" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1107万
@@ -17555,7 +17547,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1546万
@@ -17563,7 +17555,7 @@
 (25年-12月-24日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $784万
@@ -17571,7 +17563,7 @@
 (25年-11月-17日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1592万
@@ -17579,7 +17571,7 @@
 (25年-12月-05日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1298万
@@ -17587,7 +17579,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $851万
@@ -17595,7 +17587,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $578万
@@ -17603,7 +17595,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $846万
@@ -17611,7 +17603,7 @@
 (24年-12月-12日)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $923万
@@ -17619,7 +17611,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="J17" s="21" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $592万
@@ -17627,7 +17619,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="K17" s="21" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $913万
@@ -17635,7 +17627,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="L17" s="21" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1096万
@@ -17650,7 +17642,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1452万
@@ -17658,7 +17650,7 @@
 (25年-09月-23日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $808万
@@ -17666,7 +17658,7 @@
 (25年-12月-12日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1500万
@@ -17674,7 +17666,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1285万
@@ -17682,7 +17674,7 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $845万
@@ -17690,7 +17682,7 @@
 (24年-12月-16日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $572万
@@ -17698,7 +17690,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $835万
@@ -17706,7 +17698,7 @@
 (24年-12月-10日)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $1255万
@@ -17714,7 +17706,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="J18" s="21" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $586万
@@ -17722,7 +17714,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="K18" s="21" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $903万
@@ -17730,7 +17722,7 @@
 (25年-07月-31日)</t>
         </is>
       </c>
-      <c r="L18" s="21" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1055万
@@ -17745,7 +17737,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1439万
@@ -17753,7 +17745,7 @@
 (25年-10月-15日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $766万
@@ -17761,7 +17753,7 @@
 (25年-10月-28日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1465万
@@ -17769,7 +17761,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1276万
@@ -17777,7 +17769,7 @@
 (26年-04月-10日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $838万
@@ -17785,7 +17777,7 @@
 (25年-05月-15日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $566万
@@ -17793,7 +17785,7 @@
 (24年-12月-20日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $802万
@@ -17801,7 +17793,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $907万
@@ -17809,7 +17801,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="J19" s="21" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $580万
@@ -17817,7 +17809,7 @@
 (24年-12月-20日)</t>
         </is>
       </c>
-      <c r="K19" s="21" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $893万
@@ -17825,7 +17817,7 @@
 (25年-08月-01日)</t>
         </is>
       </c>
-      <c r="L19" s="21" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1074万
@@ -17840,7 +17832,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1414万
@@ -17848,7 +17840,7 @@
 (25年-10月-15日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $782万
@@ -17856,7 +17848,7 @@
 (25年-01月-16日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1447万
@@ -17864,7 +17856,7 @@
 (25年-02月-14日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1266万
@@ -17872,7 +17864,7 @@
 (25年-12月-05日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $852万
@@ -17880,7 +17872,7 @@
 (25年-01月-14日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $544万
@@ -17888,7 +17880,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $818万
@@ -17896,7 +17888,7 @@
 (24年-12月-16日)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $925万
@@ -17904,7 +17896,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $575万
@@ -17912,7 +17904,7 @@
 (24年-12月-20日)</t>
         </is>
       </c>
-      <c r="K20" s="21" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $912万
@@ -17920,7 +17912,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="L20" s="21" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1066万
@@ -17935,7 +17927,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1400万
@@ -17943,7 +17935,7 @@
 (25年-04月-29日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $753万
@@ -17951,7 +17943,7 @@
 (25年-04月-29日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1445万
@@ -17959,7 +17951,7 @@
 (25年-11月-03日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1257万
@@ -17967,7 +17959,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $841万
@@ -17975,7 +17967,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $553万
@@ -17983,7 +17975,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $811万
@@ -17991,7 +17983,7 @@
 (24年-12月-13日)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $917万
@@ -17999,7 +17991,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $570万
@@ -18007,7 +17999,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="K21" s="21" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $914万
@@ -18015,7 +18007,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="L21" s="21" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1068万
@@ -18030,7 +18022,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1446万
@@ -18038,7 +18030,7 @@
 (26年-01月-05日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $748万
@@ -18046,7 +18038,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1387万
@@ -18054,7 +18046,7 @@
 (25年-08月-01日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1248万
@@ -18062,7 +18054,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $808万
@@ -18070,7 +18062,7 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $547万
@@ -18078,7 +18070,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $781万
@@ -18086,7 +18078,7 @@
 (24年-12月-13日)</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $908万
@@ -18094,7 +18086,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $566万
@@ -18102,7 +18094,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="K22" s="21" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $881万
@@ -18110,7 +18102,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="L22" s="21" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1060万
@@ -18125,7 +18117,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1373万
@@ -18133,7 +18125,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $744万
@@ -18141,7 +18133,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1373万
@@ -18149,7 +18141,7 @@
 (25年-04月-14日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1239万
@@ -18157,7 +18149,7 @@
 (26年-02月-27日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $798万
@@ -18165,7 +18157,7 @@
 (24年-12月-13日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $540万
@@ -18173,7 +18165,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $797万
@@ -18181,7 +18173,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $1113万
@@ -18189,7 +18181,7 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="J23" s="21" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $562万
@@ -18197,7 +18189,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="K23" s="21" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $874万
@@ -18205,7 +18197,7 @@
 (25年-08月-19日)</t>
         </is>
       </c>
-      <c r="L23" s="21" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1051万
@@ -18220,7 +18212,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1418万
@@ -18228,7 +18220,7 @@
 (25年-12月-09日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $735万
@@ -18236,7 +18228,7 @@
 (25年-11月-11日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1632万
@@ -18244,7 +18236,7 @@
 (26年-03月-20日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1229万
@@ -18252,7 +18244,7 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $810万
@@ -18260,7 +18252,7 @@
 (24年-12月-16日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $519万
@@ -18268,7 +18260,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $768万
@@ -18276,7 +18268,7 @@
 (24年-12月-10日)</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $867万
@@ -18284,7 +18276,7 @@
 (24年-12月-10日)</t>
         </is>
       </c>
-      <c r="J24" s="21" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $557万
@@ -18292,7 +18284,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="K24" s="21" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $867万
@@ -18300,7 +18292,7 @@
 (25年-10月-06日)</t>
         </is>
       </c>
-      <c r="L24" s="21" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1043万
@@ -18315,7 +18307,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1346万
@@ -18323,7 +18315,7 @@
 (25年-09月-09日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $727万
@@ -18331,7 +18323,7 @@
 (25年-09月-09日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1346万
@@ -18339,7 +18331,7 @@
 (25年-11月-06日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1220万
@@ -18347,7 +18339,7 @@
 (26年-03月-10日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $777万
@@ -18355,7 +18347,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $528万
@@ -18363,7 +18355,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $783万
@@ -18371,7 +18363,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $884万
@@ -18379,7 +18371,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $553万
@@ -18387,7 +18379,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="K25" s="21" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $885万
@@ -18395,7 +18387,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="L25" s="21" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1035万
@@ -18410,7 +18402,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1333万
@@ -18418,7 +18410,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $718万
@@ -18426,7 +18418,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1333万
@@ -18434,7 +18426,7 @@
 (25年-11月-07日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1211万
@@ -18442,7 +18434,7 @@
 (26年-02月-09日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $789万
@@ -18450,7 +18442,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $521万
@@ -18458,7 +18450,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $776万
@@ -18466,7 +18458,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $876万
@@ -18474,7 +18466,7 @@
 (24年-12月-13日)</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $533万
@@ -18482,7 +18474,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="K26" s="21" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $853万
@@ -18490,7 +18482,7 @@
 (25年-03月-27日)</t>
         </is>
       </c>
-      <c r="L26" s="21" t="inlineStr">
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1026万
@@ -18505,7 +18497,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 549呎 (3房)
 $1333万
@@ -18513,7 +18505,7 @@
 (24年-12月-19日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 310呎 (1房)
 $710万
@@ -18521,7 +18513,7 @@
 (25年-10月-24日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
 $1328万
@@ -18529,7 +18521,7 @@
 (25年-11月-11日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 440呎 (2房)
 $1174万
@@ -18537,7 +18529,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 399呎 (2房)
 $775万
@@ -18545,7 +18537,7 @@
 (24年-12月-11日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
 $502万
@@ -18553,7 +18545,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 380呎 (2房)
 $769万
@@ -18561,7 +18553,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 432呎 (2房)
 $863万
@@ -18569,7 +18561,7 @@
 (24年-12月-09日)</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>J | 244呎 (1房)
 $544万
@@ -18577,7 +18569,7 @@
 (24年-12月-18日)</t>
         </is>
       </c>
-      <c r="K27" s="21" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>K | 376呎 (2房)
 $846万
@@ -18585,7 +18577,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="L27" s="21" t="inlineStr">
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>L | 434呎 (2房)
 $1018万
@@ -18600,7 +18592,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
 $2150万
@@ -18608,7 +18600,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 273呎 (1房)
 招标单位
@@ -18616,7 +18608,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 531呎 (3房)
 招标单位
@@ -18624,7 +18616,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 402呎 (2房)
 $1608万
@@ -18632,7 +18624,7 @@
 (26年-09月-17日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 358呎 (2房)
 $1432万
@@ -18640,7 +18632,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 225呎 (1房)
 $880万
@@ -18648,7 +18640,7 @@
 (26年-02月-26日)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 343呎 (2房)
 $1374万
@@ -18656,7 +18648,7 @@
 (26年-02月-26日)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 394呎 (2房)
 $1734万
@@ -18664,7 +18656,7 @@
 (26年-03月-03日)</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 204呎 (1房)
 $857万
@@ -18672,7 +18664,7 @@
 (26年-03月-12日)</t>
         </is>
       </c>
-      <c r="K28" s="21" t="inlineStr">
+      <c r="K28" s="20" t="inlineStr">
         <is>
           <t>K | 340呎 (2房)
 $1360万
@@ -18680,7 +18672,7 @@
 (26年-02月-23日)</t>
         </is>
       </c>
-      <c r="L28" s="21" t="inlineStr">
+      <c r="L28" s="20" t="inlineStr">
         <is>
           <t>L | 397呎 (2房)
 $1628万

--- a/files/港岛-北角-101 Kings Road.xlsx
+++ b/files/港岛-北角-101 Kings Road.xlsx
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1573,38 +1573,30 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>31425000</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>37500</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K16" s="5" t="n">
+        <v>31425000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>37500</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1613,7 +1605,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16406,7 +16398,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -16416,7 +16408,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -16544,12 +16536,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 838呎 (3房)
-招标单位
--
-(在售)</t>
+$3142万
+$37,500/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr"/>
@@ -16558,7 +16550,7 @@
           <t>C | 568呎 (3房)
 $1920万
 $33,799/呎
-(26年-09月-08日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">

--- a/files/港岛-北角-101 Kings Road.xlsx
+++ b/files/港岛-北角-101 Kings Road.xlsx
@@ -264,10 +264,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -821,38 +821,30 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>55950000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>50000</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K4" s="5" t="n">
+        <v>55950000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>50000</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -861,7 +853,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16069,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16093,7 +16085,7 @@
         <v>16080000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>40000</v>
+        <v>39901</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16104,7 +16096,7 @@
         <v>16080000</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>40000</v>
+        <v>39901</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -16398,7 +16390,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -16408,7 +16400,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -16506,12 +16498,12 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 1119呎 (3房)
-招标单位
--
-(在售)</t>
+$5595万
+$50,000/呎
+(26年-10月-03日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -16522,13 +16514,13 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="22" t="inlineStr"/>
-      <c r="H5" s="22" t="inlineStr"/>
-      <c r="I5" s="22" t="inlineStr"/>
-      <c r="J5" s="22" t="inlineStr"/>
-      <c r="K5" s="22" t="inlineStr"/>
-      <c r="L5" s="22" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+      <c r="K5" s="21" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -16544,7 +16536,7 @@
 (26年-09月-28日)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
@@ -16632,7 +16624,7 @@
 (26年-05月-29日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
       <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
@@ -16720,7 +16712,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr"/>
+      <c r="C8" s="21" t="inlineStr"/>
       <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
@@ -16808,7 +16800,7 @@
 (25年-04月-09日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr"/>
       <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
@@ -16896,7 +16888,7 @@
 (26年-02月-13日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr"/>
       <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
@@ -16984,7 +16976,7 @@
 (24年-12月-13日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr"/>
+      <c r="C11" s="21" t="inlineStr"/>
       <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 568呎 (3房)
@@ -18592,7 +18584,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 273呎 (1房)
 招标单位
@@ -18600,7 +18592,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 531呎 (3房)
 招标单位
@@ -18610,9 +18602,9 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>D | 402呎 (2房)
+          <t>D | 403呎 (2房)
 $1608万
-$40,000/呎
+$39,901/呎
 (26年-09月-17日)</t>
         </is>
       </c>

--- a/files/港岛-北角-101 Kings Road.xlsx
+++ b/files/港岛-北角-101 Kings Road.xlsx
@@ -13899,7 +13899,7 @@
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>5277000</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>20141</v>
+        <v>20065</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>5277000</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>20141</v>
+        <v>20065</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -18333,9 +18333,9 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>F | 262呎 (1房)
+          <t>F | 263呎 (1房)
 $528万
-$20,141/呎
+$20,065/呎
 (24年-12月-19日)</t>
         </is>
       </c>
@@ -18605,7 +18605,7 @@
           <t>D | 403呎 (2房)
 $1608万
 $39,901/呎
-(26年-09月-17日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">

--- a/files/港岛-北角-101 Kings Road.xlsx
+++ b/files/港岛-北角-101 Kings Road.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1570,14 +1570,14 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
         <v>31425000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>37500</v>
+        <v>37545</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>31425000</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>37500</v>
+        <v>37545</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -16487,7 +16487,7 @@
           <t>A | 1291呎 (4+房)
 $6455万
 $50,000/呎
-(26年-09月-19日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -16503,7 +16503,7 @@
           <t>C | 1119呎 (3房)
 $5595万
 $50,000/呎
-(26年-10月-03日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -16530,10 +16530,10 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 838呎 (3房)
+          <t>A | 837呎 (3房)
 $3142万
-$37,500/呎
-(26年-09月-28日)</t>
+$37,545/呎
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -17180,7 +17180,7 @@
           <t>D | 440呎 (2房)
 $1502万
 $34,143/呎
-(26年-09月-19日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">

--- a/files/港岛-北角-101 Kings Road.xlsx
+++ b/files/港岛-北角-101 Kings Road.xlsx
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>31425000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>37545</v>
+        <v>37500</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>31425000</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>37545</v>
+        <v>37500</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>5277000</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>20065</v>
+        <v>20141</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>5277000</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>20065</v>
+        <v>20141</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>16080000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>39901</v>
+        <v>40000</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>16080000</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>39901</v>
+        <v>40000</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -16530,9 +16530,9 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 837呎 (3房)
+          <t>A | 838呎 (3房)
 $3142万
-$37,545/呎
+$37,500/呎
 (26年-10月-16日)</t>
         </is>
       </c>
@@ -18333,9 +18333,9 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>F | 263呎 (1房)
+          <t>F | 262呎 (1房)
 $528万
-$20,065/呎
+$20,141/呎
 (24年-12月-19日)</t>
         </is>
       </c>
@@ -18602,9 +18602,9 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>D | 403呎 (2房)
+          <t>D | 402呎 (2房)
 $1608万
-$39,901/呎
+$40,000/呎
 (26年-10月-05日)</t>
         </is>
       </c>
